--- a/artfynd/A 9495-2025 artfynd.xlsx
+++ b/artfynd/A 9495-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71931664</v>
+        <v>71931629</v>
       </c>
       <c r="B2" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,31 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödkärr, N om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592735.1488773545</v>
+        <v>592715</v>
       </c>
       <c r="R2" t="n">
-        <v>6575894.408387265</v>
+        <v>6575884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,21 +743,11 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -788,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>slänt, f d järnvägsvall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,12 +780,7 @@
         <v>71931665</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592724.9222416993</v>
+        <v>592725</v>
       </c>
       <c r="R3" t="n">
-        <v>6575894.15829848</v>
+        <v>6575894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +845,9 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>71931645</v>
+        <v>71931687</v>
       </c>
       <c r="B4" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,16 +890,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,31 +907,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödkärr, N om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592745.6007695735</v>
+        <v>592644</v>
       </c>
       <c r="R4" t="n">
-        <v>6575864.530171866</v>
+        <v>6575963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,19 +947,9 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-06-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>71931641</v>
+        <v>71931634</v>
       </c>
       <c r="B5" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1011,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1108,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592765.5310186908</v>
+        <v>592736</v>
       </c>
       <c r="R5" t="n">
-        <v>6575844.587826174</v>
+        <v>6575855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,21 +1063,11 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1167,7 +1079,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Lövskogsbryn mot åker</t>
+          <t>slänt, f d järnvägsvall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1185,32 +1097,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71931661</v>
+        <v>71931635</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>220320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1218,17 +1125,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödkärr, N om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592735.1488773545</v>
+        <v>592796</v>
       </c>
       <c r="R6" t="n">
-        <v>6575894.408387265</v>
+        <v>6575835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,21 +1179,11 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1284,7 +1195,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lövskogsbryn mot åker</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1302,15 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>71931655</v>
+        <v>71931637</v>
       </c>
       <c r="B7" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1243,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1356,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592725.1593968171</v>
+        <v>592786</v>
       </c>
       <c r="R7" t="n">
-        <v>6575884.460007075</v>
+        <v>6575835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,21 +1295,11 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1415,7 +1311,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lövskogsbryn mot åker</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1433,15 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>71931667</v>
+        <v>71931638</v>
       </c>
       <c r="B8" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1359,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1487,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592724.9222416993</v>
+        <v>592776</v>
       </c>
       <c r="R8" t="n">
-        <v>6575894.15829848</v>
+        <v>6575835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1520,21 +1411,11 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1546,7 +1427,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lövskogsbryn mot åker</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1564,15 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>71931651</v>
+        <v>71931641</v>
       </c>
       <c r="B9" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1475,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1618,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592725.4090342049</v>
+        <v>592766</v>
       </c>
       <c r="R9" t="n">
-        <v>6575874.251252572</v>
+        <v>6575845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1651,21 +1527,11 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1677,7 +1543,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lövskogsbryn mot åker</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1692,6 +1558,1268 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>71931644</v>
+      </c>
+      <c r="B10" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>592745</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6575854</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>71931645</v>
+      </c>
+      <c r="B11" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>592746</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6575865</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>71931649</v>
+      </c>
+      <c r="B12" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>592735</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6575864</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>71931651</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>592725</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6575874</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>71931655</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>592725</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6575884</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>71931664</v>
+      </c>
+      <c r="B15" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>592735</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6575894</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>71931667</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>592725</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6575894</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>71931668</v>
+      </c>
+      <c r="B17" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592715</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6575884</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>71931672</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592675</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6575924</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>slänt, f d järnvägsvall</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>71931688</v>
+      </c>
+      <c r="B19" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>592644</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6575963</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>71931661</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rödkärr, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>592735</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6575894</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-06-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9495-2025 artfynd.xlsx
+++ b/artfynd/A 9495-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931665</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931687</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931634</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931635</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931637</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931638</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931641</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931644</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1790,6 +1840,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931645</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1906,6 +1961,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931649</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2022,6 +2082,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931651</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2138,6 +2203,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931655</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2254,6 +2324,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931664</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2370,6 +2445,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931667</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2486,6 +2566,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931668</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2602,6 +2687,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931672</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2718,6 +2808,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931688</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2820,8 +2915,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71931661</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>